--- a/planer/Resources/Zeiterfassung.xlsx
+++ b/planer/Resources/Zeiterfassung.xlsx
@@ -368,8 +368,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;BZeiterfassungen August 2024 - Anny, Dutly &amp;RStand: Sonntag, 11.08.24, 16:40 Uhr</oddHeader>
-    <oddFooter>&amp;LGeneriert via schichtplaner-online.de</oddFooter>
+    <oddFooter>&amp;LSchichtplaner</oddFooter>
   </headerFooter>
 </worksheet>
 </file>